--- a/tame_output/ON/bt/strategyON_20231209.xlsx
+++ b/tame_output/ON/bt/strategyON_20231209.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>74.8%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-268.8%</t>
+          <t>-308.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>486.1%</t>
+          <t>480.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-109.6%</t>
+          <t>-137.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-61.7%</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-96.0%</t>
+          <t>-111.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1130,47 +1130,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.5%</t>
+          <t>103.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -41927,10 +41927,10 @@
         <v>2.968547780644436</v>
       </c>
       <c r="D1757" t="n">
-        <v>-1.080609411585992</v>
+        <v>-1.477640073019202</v>
       </c>
       <c r="E1757" t="n">
-        <v>2.535947591696293</v>
+        <v>2.377135327123009</v>
       </c>
       <c r="F1757" t="n">
         <v>1.04617033602595</v>
@@ -41950,10 +41950,10 @@
         <v>2.965146865274802</v>
       </c>
       <c r="D1758" t="n">
-        <v>-1.076100063360206</v>
+        <v>-1.473130724793417</v>
       </c>
       <c r="E1758" t="n">
-        <v>2.534350415616973</v>
+        <v>2.375538151043689</v>
       </c>
       <c r="F1758" t="n">
         <v>1.04617033602595</v>
@@ -41973,10 +41973,10 @@
         <v>2.964689051375926</v>
       </c>
       <c r="D1759" t="n">
-        <v>-1.086407189017642</v>
+        <v>-1.483437850450852</v>
       </c>
       <c r="E1759" t="n">
-        <v>2.529769751455123</v>
+        <v>2.370957486881839</v>
       </c>
       <c r="F1759" t="n">
         <v>1.039171953711096</v>
@@ -41996,10 +41996,10 @@
         <v>2.992474709334104</v>
       </c>
       <c r="D1760" t="n">
-        <v>-1.134649837903354</v>
+        <v>-1.531680499336564</v>
       </c>
       <c r="E1760" t="n">
-        <v>2.538258349859016</v>
+        <v>2.379446085285732</v>
       </c>
       <c r="F1760" t="n">
         <v>1.039171953711096</v>
@@ -42019,10 +42019,10 @@
         <v>3.010249418375564</v>
       </c>
       <c r="D1761" t="n">
-        <v>-1.127551836935852</v>
+        <v>-1.524582498369062</v>
       </c>
       <c r="E1761" t="n">
-        <v>2.558872259287476</v>
+        <v>2.400059994714192</v>
       </c>
       <c r="F1761" t="n">
         <v>1.039279151822472</v>
@@ -42042,10 +42042,10 @@
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>-1.126348770639745</v>
+        <v>-1.523379432072956</v>
       </c>
       <c r="E1762" t="n">
-        <v>2.559827045486959</v>
+        <v>2.401014780913675</v>
       </c>
       <c r="F1762" t="n">
         <v>1.039279151822472</v>
@@ -42065,10 +42065,10 @@
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>-1.1239957233065</v>
+        <v>-1.52102638473971</v>
       </c>
       <c r="E1763" t="n">
-        <v>2.566107636557155</v>
+        <v>2.407295371983871</v>
       </c>
       <c r="F1763" t="n">
         <v>1.041632199155718</v>
@@ -42088,10 +42088,10 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>-1.122879441315274</v>
+        <v>-1.519910102748484</v>
       </c>
       <c r="E1764" t="n">
-        <v>2.581131174189695</v>
+        <v>2.422318909616411</v>
       </c>
       <c r="F1764" t="n">
         <v>1.042748481146944</v>
@@ -42111,10 +42111,10 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>-1.119141485254219</v>
+        <v>-1.516172146687429</v>
       </c>
       <c r="E1765" t="n">
-        <v>2.582551337477764</v>
+        <v>2.42373907290448</v>
       </c>
       <c r="F1765" t="n">
         <v>1.045124933427569</v>
@@ -42134,10 +42134,10 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>-1.110644339593086</v>
+        <v>-1.507675001026296</v>
       </c>
       <c r="E1766" t="n">
-        <v>2.584265620240312</v>
+        <v>2.425453355667028</v>
       </c>
       <c r="F1766" t="n">
         <v>1.045124933427569</v>
@@ -42157,10 +42157,10 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-1.110336379508361</v>
+        <v>-1.507367040941571</v>
       </c>
       <c r="E1767" t="n">
-        <v>2.588777379955048</v>
+        <v>2.429965115381764</v>
       </c>
       <c r="F1767" t="n">
         <v>1.046306647520268</v>
@@ -42180,10 +42180,10 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-1.10855461713777</v>
+        <v>-1.50558527857098</v>
       </c>
       <c r="E1768" t="n">
-        <v>2.591150382080159</v>
+        <v>2.432338117506875</v>
       </c>
       <c r="F1768" t="n">
         <v>1.046306647520268</v>
@@ -42203,10 +42203,10 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-1.112631972274861</v>
+        <v>-1.509662633708071</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.604553610289012</v>
+        <v>2.445741345715728</v>
       </c>
       <c r="F1769" t="n">
         <v>1.046306647520268</v>
@@ -42226,10 +42226,10 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-1.102639891348452</v>
+        <v>-1.499670552781662</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.606864877323709</v>
+        <v>2.448052612750425</v>
       </c>
       <c r="F1770" t="n">
         <v>1.056298728446678</v>
@@ -42249,10 +42249,10 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-1.10319564640449</v>
+        <v>-1.5002263078377</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.609544385197885</v>
+        <v>2.450732120624601</v>
       </c>
       <c r="F1771" t="n">
         <v>1.0546913146856</v>
@@ -42272,10 +42272,10 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-1.106409998817801</v>
+        <v>-1.503440660251011</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.613783633371708</v>
+        <v>2.454971368798424</v>
       </c>
       <c r="F1772" t="n">
         <v>1.0546913146856</v>
@@ -42295,10 +42295,10 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-1.123418244220411</v>
+        <v>-1.520448905653621</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.608057907848395</v>
+        <v>2.449245643275111</v>
       </c>
       <c r="F1773" t="n">
         <v>1.057690449698574</v>
@@ -42312,16 +42312,16 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066013</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-1.104458521769056</v>
+        <v>-1.501489183202266</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.61639165900021</v>
+        <v>2.457579394426926</v>
       </c>
       <c r="F1774" t="n">
         <v>1.057690449698574</v>
@@ -42335,16 +42335,16 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293022</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-1.103223797166247</v>
+        <v>-1.500254458599457</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.615121146304915</v>
+        <v>2.456308881731631</v>
       </c>
       <c r="F1775" t="n">
         <v>1.057690449698574</v>
@@ -42358,16 +42358,16 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239775</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-1.113258060989896</v>
+        <v>-1.510288722423106</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.614675050612317</v>
+        <v>2.455862786039033</v>
       </c>
       <c r="F1776" t="n">
         <v>1.057690449698574</v>
@@ -42387,10 +42387,10 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-1.118297059287762</v>
+        <v>-1.515327720720972</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.636641413182779</v>
+        <v>2.477829148609495</v>
       </c>
       <c r="F1777" t="n">
         <v>1.052651451400707</v>
@@ -42404,16 +42404,16 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-1.108477341127212</v>
+        <v>-1.505508002560422</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.638038011934229</v>
+        <v>2.479225747360945</v>
       </c>
       <c r="F1778" t="n">
         <v>1.059081391617394</v>
@@ -42427,16 +42427,16 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-1.106675714288258</v>
+        <v>-1.503706375721468</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.624007224673437</v>
+        <v>2.465194960100153</v>
       </c>
       <c r="F1779" t="n">
         <v>1.059081391617394</v>
@@ -42450,16 +42450,16 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-1.10568703254409</v>
+        <v>-1.5027176939773</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.622516453686776</v>
+        <v>2.463704189113492</v>
       </c>
       <c r="F1780" t="n">
         <v>1.059081391617394</v>
@@ -42473,16 +42473,16 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-1.097690678022551</v>
+        <v>-1.494721339455761</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.627688621951231</v>
+        <v>2.468876357377948</v>
       </c>
       <c r="F1781" t="n">
         <v>1.067077746138933</v>
@@ -42496,16 +42496,16 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-1.092706927350642</v>
+        <v>-1.489737588783852</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.641520702810907</v>
+        <v>2.482708438237623</v>
       </c>
       <c r="F1782" t="n">
         <v>1.072061496810842</v>
@@ -42519,16 +42519,16 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597767</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-1.086320788401087</v>
+        <v>-1.483351449834297</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.650803361402518</v>
+        <v>2.491991096829234</v>
       </c>
       <c r="F1783" t="n">
         <v>1.072061496810842</v>
@@ -42542,16 +42542,16 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527686</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-1.09812613871972</v>
+        <v>-1.49515680015293</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.650097310034607</v>
+        <v>2.491285045461324</v>
       </c>
       <c r="F1784" t="n">
         <v>1.060256146492209</v>
@@ -42565,16 +42565,16 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-1.089394327941053</v>
+        <v>-1.486424989374263</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.659537491955963</v>
+        <v>2.500725227382679</v>
       </c>
       <c r="F1785" t="n">
         <v>1.068987957270875</v>
@@ -42594,10 +42594,10 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-1.083057441296601</v>
+        <v>-1.480088102729811</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.657383065561729</v>
+        <v>2.498570800988445</v>
       </c>
       <c r="F1786" t="n">
         <v>1.068987957270875</v>
@@ -42611,16 +42611,16 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-1.080522993569233</v>
+        <v>-1.477553655002443</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.668359502454871</v>
+        <v>2.509547237881586</v>
       </c>
       <c r="F1787" t="n">
         <v>1.068987957270875</v>
@@ -42634,16 +42634,16 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-1.080598892549838</v>
+        <v>-1.477629553983048</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.660743823055538</v>
+        <v>2.501931558482255</v>
       </c>
       <c r="F1788" t="n">
         <v>1.069751217960202</v>
@@ -42657,16 +42657,16 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-1.091101082109184</v>
+        <v>-1.488131743542394</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.634307523022173</v>
+        <v>2.475495258448889</v>
       </c>
       <c r="F1789" t="n">
         <v>1.059249028400855</v>
@@ -42680,16 +42680,16 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487809</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-1.0929343447883</v>
+        <v>-1.48996500622151</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.634275057796649</v>
+        <v>2.475462793223364</v>
       </c>
       <c r="F1790" t="n">
         <v>1.059249028400855</v>
@@ -42703,16 +42703,16 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823381</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-1.097943459849885</v>
+        <v>-1.494974121283094</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.632788491600874</v>
+        <v>2.47397622702759</v>
       </c>
       <c r="F1791" t="n">
         <v>1.058254450842321</v>
@@ -42726,16 +42726,16 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-1.101649016486699</v>
+        <v>-1.498679677919909</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.630533994186514</v>
+        <v>2.471721729613229</v>
       </c>
       <c r="F1792" t="n">
         <v>1.056384775584686</v>
@@ -42749,16 +42749,16 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-1.100416691129334</v>
+        <v>-1.497447352562544</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.631446776391779</v>
+        <v>2.472634511818495</v>
       </c>
       <c r="F1793" t="n">
         <v>1.057015151956723</v>
@@ -42772,16 +42772,16 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714844</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-1.090088694113481</v>
+        <v>-1.487119355546691</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.639707883362334</v>
+        <v>2.48089561878905</v>
       </c>
       <c r="F1794" t="n">
         <v>1.067343148972576</v>
@@ -42795,16 +42795,16 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083877</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-1.089972358965926</v>
+        <v>-1.487003020399136</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.646275077623192</v>
+        <v>2.487462813049908</v>
       </c>
       <c r="F1795" t="n">
         <v>1.067459484120131</v>
@@ -42818,16 +42818,16 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666734</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-1.091817768542793</v>
+        <v>-1.488848429976003</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.642510884237834</v>
+        <v>2.48369861966455</v>
       </c>
       <c r="F1796" t="n">
         <v>1.067459484120131</v>
@@ -42841,16 +42841,16 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097099</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-1.090319336017694</v>
+        <v>-1.487349997450904</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.643048545109007</v>
+        <v>2.484236280535723</v>
       </c>
       <c r="F1797" t="n">
         <v>1.06895791664523</v>
@@ -42864,16 +42864,16 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762259</v>
+        <v>3.169279212762258</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-1.098383588210428</v>
+        <v>-1.495414249643638</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.641100822175225</v>
+        <v>2.482288557601941</v>
       </c>
       <c r="F1798" t="n">
         <v>1.060893664452496</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-1.099713555671641</v>
+        <v>-1.496744217104851</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.64056883519074</v>
+        <v>2.481756570617456</v>
       </c>
       <c r="F1799" t="n">
         <v>1.060893664452496</v>
@@ -42910,16 +42910,16 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583695</v>
+        <v>3.199276732583694</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-0.8718488729381295</v>
+        <v>-1.268879534371339</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.733931181391306</v>
+        <v>2.575118916818022</v>
       </c>
       <c r="F1800" t="n">
         <v>1.060893664452496</v>
@@ -42933,16 +42933,16 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742725</v>
+        <v>3.238767863742724</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-0.6237473090709127</v>
+        <v>-1.020777970504123</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.840706403283285</v>
+        <v>2.681894138710001</v>
       </c>
       <c r="F1801" t="n">
         <v>1.060893664452496</v>
@@ -42956,16 +42956,16 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589525</v>
+        <v>3.260068416589524</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-0.3269089096775823</v>
+        <v>-0.7239395711107923</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.960864774014075</v>
+        <v>2.802052509440791</v>
       </c>
       <c r="F1802" t="n">
         <v>1.175748152933624</v>
@@ -42979,16 +42979,16 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872958</v>
+        <v>3.306739876872957</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-0.02326935285214582</v>
+        <v>-0.4203000142853558</v>
       </c>
       <c r="E1803" t="n">
-        <v>3.083997671209936</v>
+        <v>2.925185406636652</v>
       </c>
       <c r="F1803" t="n">
         <v>1.175748152933624</v>
@@ -43002,16 +43002,16 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.31216459594633</v>
+        <v>3.312164595946329</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>0.2657512535885628</v>
+        <v>-0.1312794078446472</v>
       </c>
       <c r="E1804" t="n">
-        <v>3.195545335235677</v>
+        <v>3.036733070662393</v>
       </c>
       <c r="F1804" t="n">
         <v>1.175748152933624</v>
@@ -43031,10 +43031,10 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>0.5504711808524599</v>
+        <v>0.15344051941925</v>
       </c>
       <c r="E1805" t="n">
-        <v>3.314653445485253</v>
+        <v>3.15584118091197</v>
       </c>
       <c r="F1805" t="n">
         <v>1.460468080197521</v>
@@ -43048,16 +43048,16 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>2.961321289647559</v>
+        <v>2.983306949052795</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>0.8349621307712132</v>
+        <v>0.8070806264286061</v>
       </c>
       <c r="E1806" t="n">
-        <v>3.433761988626562</v>
+        <v>3.422609386889519</v>
       </c>
       <c r="F1806" t="n">
         <v>1.460468080197521</v>

--- a/tame_output/ON/bt/strategyON_20231209.xlsx
+++ b/tame_output/ON/bt/strategyON_20231209.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-61.7%</t>
+          <t>-61.8%</t>
         </is>
       </c>
     </row>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>0.8070806264286061</v>
+        <v>0.8064405048670571</v>
       </c>
       <c r="E1806" t="n">
-        <v>3.422609386889519</v>
+        <v>3.422353338264899</v>
       </c>
       <c r="F1806" t="n">
         <v>1.460468080197521</v>

--- a/tame_output/ON/bt/strategyON_20231209.xlsx
+++ b/tame_output/ON/bt/strategyON_20231209.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>480.6%</t>
+          <t>476.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-61.8%</t>
+          <t>-98.7%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1140,32 +1140,32 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
     </row>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.91290325494784</v>
+        <v>2.912903254947839</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -41967,7 +41967,7 @@
         <v>45221</v>
       </c>
       <c r="B1759" t="n">
-        <v>2.940632196767551</v>
+        <v>2.94063219676755</v>
       </c>
       <c r="C1759" t="n">
         <v>2.964689051375926</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055149</v>
+        <v>3.048806209055148</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597767</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527686</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844645</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487809</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.14626574482338</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714844</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083876</v>
+        <v>3.136752015083877</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666733</v>
+        <v>3.162269743666734</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097098</v>
+        <v>3.163432091097099</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762258</v>
+        <v>3.169279212762259</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>0.8064405048670571</v>
+        <v>0.4372021889107903</v>
       </c>
       <c r="E1806" t="n">
-        <v>3.422353338264899</v>
+        <v>3.274658011882392</v>
       </c>
       <c r="F1806" t="n">
         <v>1.460468080197521</v>

--- a/tame_output/ON/bt/strategyON_20231209.xlsx
+++ b/tame_output/ON/bt/strategyON_20231209.xlsx
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.912903254947839</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -41967,7 +41967,7 @@
         <v>45221</v>
       </c>
       <c r="B1759" t="n">
-        <v>2.94063219676755</v>
+        <v>2.940632196767551</v>
       </c>
       <c r="C1759" t="n">
         <v>2.964689051375926</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055148</v>
+        <v>3.048806209055149</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
